--- a/Team-Data/2013-14/3-29-2013-14.xlsx
+++ b/Team-Data/2013-14/3-29-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.431</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,7 +746,7 @@
         <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
         <v>0.455</v>
@@ -688,25 +755,25 @@
         <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O2" t="n">
         <v>16.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
         <v>39.9</v>
@@ -721,7 +788,7 @@
         <v>8.4</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
@@ -733,13 +800,13 @@
         <v>19.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC2" t="n">
         <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -775,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -808,10 +875,10 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1133,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
@@ -1145,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1333,7 +1400,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>27</v>
@@ -1503,7 +1570,7 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1533,7 +1600,7 @@
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
         <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0.595</v>
+        <v>0.589</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.473</v>
@@ -1783,19 +1850,19 @@
         <v>22.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O8" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0.797</v>
       </c>
       <c r="R8" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
         <v>30.6</v>
@@ -1807,7 +1874,7 @@
         <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.800000000000001</v>
@@ -1822,19 +1889,19 @@
         <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB8" t="n">
         <v>104.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
@@ -1843,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1861,13 +1928,13 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1879,10 +1946,10 @@
         <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>5</v>
@@ -1897,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2055,7 +2122,7 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>8</v>
@@ -2070,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L10" t="n">
         <v>6</v>
@@ -2150,13 +2217,13 @@
         <v>0.317</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.668</v>
+        <v>0.666</v>
       </c>
       <c r="R10" t="n">
         <v>14.2</v>
@@ -2165,7 +2232,7 @@
         <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
@@ -2189,13 +2256,13 @@
         <v>20.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2216,10 +2283,10 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2243,13 +2310,13 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2258,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2398,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2446,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.681</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J12" t="n">
         <v>79.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L12" t="n">
         <v>9.300000000000001</v>
@@ -2511,16 +2578,16 @@
         <v>26.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O12" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.703</v>
+        <v>0.701</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2529,10 +2596,10 @@
         <v>33.9</v>
       </c>
       <c r="T12" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="U12" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2541,34 +2608,34 @@
         <v>7.5</v>
       </c>
       <c r="X12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
         <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="AB12" t="n">
         <v>107</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>16</v>
@@ -2616,7 +2683,7 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>5.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2753,7 +2820,7 @@
         <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2777,7 +2844,7 @@
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.703</v>
+        <v>0.699</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O14" t="n">
         <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
@@ -2896,37 +2963,37 @@
         <v>42.8</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y14" t="n">
         <v>3.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA14" t="n">
         <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.5</v>
+        <v>107.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -2992,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
@@ -3135,7 +3202,7 @@
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3144,7 +3211,7 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.694</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J17" t="n">
         <v>76.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="L17" t="n">
         <v>8</v>
@@ -3421,55 +3488,55 @@
         <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O17" t="n">
         <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.76</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="S17" t="n">
         <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="U17" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
         <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>103</v>
+        <v>103.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3538,13 +3605,13 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3573,85 +3640,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>0.192</v>
+        <v>0.194</v>
       </c>
       <c r="H18" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N18" t="n">
         <v>0.355</v>
       </c>
       <c r="O18" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R18" t="n">
         <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T18" t="n">
         <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W18" t="n">
         <v>6.8</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,13 +3736,13 @@
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>21</v>
@@ -3687,19 +3754,19 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT18" t="n">
         <v>23</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>24</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3878,13 +3945,13 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -3937,70 +4004,70 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J20" t="n">
         <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
         <v>5.9</v>
       </c>
       <c r="M20" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
         <v>18.1</v>
       </c>
       <c r="P20" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0.771</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>22.8</v>
@@ -4009,13 +4076,13 @@
         <v>20.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
@@ -4036,7 +4103,7 @@
         <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4045,25 +4112,25 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4245,7 +4312,7 @@
         <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
@@ -4254,13 +4321,13 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,19 +4458,19 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4576,10 +4643,10 @@
         <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>57</v>
       </c>
       <c r="G24" t="n">
-        <v>0.219</v>
+        <v>0.208</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J24" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -4695,16 +4762,16 @@
         <v>22.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>0.307</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
         <v>23.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R24" t="n">
         <v>12</v>
@@ -4716,7 +4783,7 @@
         <v>43.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V24" t="n">
         <v>17.2</v>
@@ -4737,13 +4804,13 @@
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>99</v>
+        <v>98.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11</v>
+        <v>-11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4764,10 +4831,10 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="n">
         <v>12</v>
@@ -4776,16 +4843,16 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4937,13 +5004,13 @@
         <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5143,7 +5210,7 @@
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G27" t="n">
-        <v>0.342</v>
+        <v>0.347</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J27" t="n">
         <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N27" t="n">
         <v>0.337</v>
       </c>
       <c r="O27" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R27" t="n">
         <v>12.2</v>
@@ -5259,19 +5326,19 @@
         <v>32.2</v>
       </c>
       <c r="T27" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U27" t="n">
         <v>18.9</v>
       </c>
       <c r="V27" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W27" t="n">
         <v>7.2</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.6</v>
@@ -5280,16 +5347,16 @@
         <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB27" t="n">
         <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5304,13 +5371,13 @@
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5331,7 +5398,7 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS27" t="n">
         <v>13</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
@@ -5358,7 +5425,7 @@
         <v>29</v>
       </c>
       <c r="BA27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="J28" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
         <v>8.5</v>
@@ -5432,7 +5499,7 @@
         <v>20.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R28" t="n">
         <v>9.1</v>
@@ -5453,10 +5520,10 @@
         <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
         <v>18.2</v>
@@ -5465,13 +5532,13 @@
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>19</v>
@@ -5534,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5683,7 +5750,7 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5725,7 +5792,7 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5871,7 +5938,7 @@
         <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ30" t="n">
         <v>23</v>
@@ -5898,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
         <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.521</v>
+        <v>0.514</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
@@ -5957,16 +6024,16 @@
         <v>38.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L31" t="n">
         <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N31" t="n">
         <v>0.385</v>
@@ -5990,7 +6057,7 @@
         <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
         <v>14.7</v>
@@ -6002,7 +6069,7 @@
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
         <v>20.5</v>
@@ -6017,10 +6084,10 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
         <v>15</v>
@@ -6041,7 +6108,7 @@
         <v>13</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-29-2013-14</t>
+          <t>2014-03-29</t>
         </is>
       </c>
     </row>
